--- a/data/报告数据.xlsx
+++ b/data/报告数据.xlsx
@@ -7,9 +7,9 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_全局信息" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="data.shareholders" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="data.shareholder_info" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="date.全局信息" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="form.股东出资" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="form.股东信息" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,7 +437,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>g.company_name</t>
+          <t>date.公司名</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -449,7 +449,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>g.credit_code</t>
+          <t>date.信用代码</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -461,7 +461,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>g.registered_address</t>
+          <t>date.注册地址</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -473,7 +473,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>g.legal_representative</t>
+          <t>date.法定代表人</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -485,7 +485,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>g.company_type</t>
+          <t>date.公司类型</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -497,7 +497,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>g.registered_capital</t>
+          <t>date.注册资本</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -507,7 +507,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>g.business_scope</t>
+          <t>date.经营范围</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -519,7 +519,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>g.established_date</t>
+          <t>date.成立日期</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -531,7 +531,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>g.operating_period</t>
+          <t>date.经营期限</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -564,27 +564,27 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>shareholder_name</t>
+          <t>股东</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>subscribed_amount</t>
+          <t>认缴金额</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>subscribed_ratio</t>
+          <t>认缴比例</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>paid_amount</t>
+          <t>实缴金额</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>paid_ratio</t>
+          <t>实缴比例</t>
         </is>
       </c>
     </row>
@@ -666,12 +666,12 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>序号</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>detail</t>
+          <t>详情</t>
         </is>
       </c>
     </row>

--- a/data/报告数据.xlsx
+++ b/data/报告数据.xlsx
@@ -8,8 +8,10 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="date.全局信息" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="form.股东出资" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="form.股东信息" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="date.基本情况" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="form.股东出资" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="form.股东信息" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="form.投资明细" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -415,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -437,106 +439,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>date.公司名</t>
+          <t>date.全局信息.公司名</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>深圳市创新科技有限公司</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>date.信用代码</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>91440300MA5XXXXX00</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>date.注册地址</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>深圳市南山区粤海街道科技园南路88号</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>date.法定代表人</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>张伟</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>date.公司类型</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>有限责任公司</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>date.注册资本</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>date.经营范围</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>软件开发、技术咨询、技术服务</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>date.成立日期</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2018-06-15</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>date.经营期限</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2018-06-15 至 长期</t>
         </is>
       </c>
     </row>
@@ -546,6 +454,130 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>字段编码</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>值</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>date.基本情况.信用代码</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>91440300MA5XXXXX00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>date.基本情况.注册地址</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>深圳市南山区粤海街道科技园南路88号</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>date.基本情况.法定代表人</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>张伟</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>date.基本情况.公司类型</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>有限责任公司</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>date.基本情况.注册资本</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>date.基本情况.经营范围</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>软件开发、技术咨询、技术服务</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>date.基本情况.成立日期</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2018-06-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>date.基本情况.经营期限</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2018-06-15 至 长期</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -650,7 +682,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -671,7 +703,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>详情</t>
+          <t>职务</t>
         </is>
       </c>
     </row>
@@ -703,6 +735,94 @@
         <is>
           <t>王强-股东</t>
         </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>项目</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>金额</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>比例</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>项目A</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>500</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>项目B</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>300</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>项目C</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>200</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>合计</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/data/报告数据.xlsx
+++ b/data/报告数据.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="date.全局信息" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="date.基本情况" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="form.股东出资" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="form.股东信息" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="form.员工信息" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="form.投资明细" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
@@ -439,7 +439,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>date.全局信息.公司名</t>
+          <t>公司名</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -481,7 +481,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>date.基本情况.信用代码</t>
+          <t>信用代码</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -493,7 +493,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>date.基本情况.注册地址</t>
+          <t>注册地址</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -505,7 +505,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>date.基本情况.法定代表人</t>
+          <t>法定代表人</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -517,7 +517,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>date.基本情况.公司类型</t>
+          <t>公司类型</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -529,7 +529,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>date.基本情况.注册资本</t>
+          <t>注册资本</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -539,7 +539,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>date.基本情况.经营范围</t>
+          <t>经营范围</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -551,7 +551,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>date.基本情况.成立日期</t>
+          <t>成立日期</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -563,7 +563,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>date.基本情况.经营期限</t>
+          <t>经营期限</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>比例</t>
+          <t>持股比例</t>
         </is>
       </c>
     </row>

--- a/data/报告数据.xlsx
+++ b/data/报告数据.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -569,6 +569,18 @@
       <c r="B9" t="inlineStr">
         <is>
           <t>2018-06-15 至 长期</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>有职工信息</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>FALSE</t>
         </is>
       </c>
     </row>

--- a/data/报告数据.xlsx
+++ b/data/报告数据.xlsx
@@ -702,10 +702,6 @@
   </sheetPr>
   <dimension ref="A1:B4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -762,11 +758,6 @@
   </sheetPr>
   <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
